--- a/data/trans_orig/AIRE_2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_2-Habitat-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8785</t>
+          <t>9554</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>410</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>6069</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2484</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11321</t>
+          <t>11513</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5662</t>
+          <t>5708</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13879</t>
+          <t>13579</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3765</t>
+          <t>4639</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13451</t>
+          <t>14956</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>11910</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25257</t>
+          <t>23955</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10636</t>
+          <t>10960</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20168</t>
+          <t>20109</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14888</t>
+          <t>14791</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26477</t>
+          <t>26595</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28654</t>
+          <t>28371</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>44526</t>
+          <t>44154</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,02%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8444</t>
+          <t>9066</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14405</t>
+          <t>13327</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7843</t>
+          <t>7748</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19875</t>
+          <t>19733</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,91%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12954</t>
+          <t>13069</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5359</t>
+          <t>5535</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15418</t>
+          <t>15714</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12542</t>
+          <t>12305</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25133</t>
+          <t>24564</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2236</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9495</t>
+          <t>9707</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3945</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14834</t>
+          <t>14715</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7717</t>
+          <t>7673</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20970</t>
+          <t>20260</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7790</t>
+          <t>7776</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18059</t>
+          <t>18103</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11855</t>
+          <t>12587</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25954</t>
+          <t>26694</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22812</t>
+          <t>23166</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>39984</t>
+          <t>41479</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>25,3%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25720</t>
+          <t>25944</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38663</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33153</t>
+          <t>32966</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51626</t>
+          <t>51126</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>63453</t>
+          <t>64219</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>85979</t>
+          <t>85651</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,24%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>5765</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15132</t>
+          <t>15106</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14648</t>
+          <t>15352</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30425</t>
+          <t>30502</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24097</t>
+          <t>24271</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41272</t>
+          <t>42140</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,7%</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9878</t>
+          <t>10062</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>4935</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15276</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9167</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20432</t>
+          <t>20602</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,57%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10393</t>
+          <t>10285</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10528</t>
+          <t>10159</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>4792</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17001</t>
+          <t>17684</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18509</t>
+          <t>19801</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61961</t>
+          <t>62518</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>16547</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32020</t>
+          <t>31893</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43869</t>
+          <t>43326</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>96803</t>
+          <t>101934</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>72,67%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>7170</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35193</t>
+          <t>34511</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20126</t>
+          <t>21212</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>36124</t>
+          <t>36682</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25806</t>
+          <t>25692</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>64757</t>
+          <t>65322</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,57%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12665</t>
+          <t>12256</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>2964</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12837</t>
+          <t>12341</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6363</t>
+          <t>5830</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21467</t>
+          <t>20476</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>14,6%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>492</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8533</t>
+          <t>8214</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>813</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7574</t>
+          <t>8478</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>530</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>5772</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1681</t>
+          <t>1652</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10738</t>
+          <t>10331</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3092</t>
+          <t>3214</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12858</t>
+          <t>13253</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>9404</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22066</t>
+          <t>22941</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>13775</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>27306</t>
+          <t>27300</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25887</t>
+          <t>25793</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>45425</t>
+          <t>44375</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,13%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19854</t>
+          <t>20227</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>33933</t>
+          <t>34108</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17505</t>
+          <t>17087</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30964</t>
+          <t>30990</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>41276</t>
+          <t>41653</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>61799</t>
+          <t>60662</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>43,92%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9446</t>
+          <t>9536</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21453</t>
+          <t>20993</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4782</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14968</t>
+          <t>15499</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16418</t>
+          <t>16730</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>32031</t>
+          <t>32175</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,3%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8257</t>
+          <t>7904</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20467</t>
+          <t>19659</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15333</t>
+          <t>15467</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>15417</t>
+          <t>15850</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>31495</t>
+          <t>30782</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8604</t>
+          <t>9154</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>23235</t>
+          <t>24443</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13180</t>
+          <t>13446</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>29865</t>
+          <t>29446</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>26045</t>
+          <t>25795</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>48235</t>
+          <t>46620</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>50871</t>
+          <t>51338</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>138388</t>
+          <t>142413</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>58080</t>
+          <t>58500</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>84479</t>
+          <t>85366</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>119905</t>
+          <t>121665</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>213505</t>
+          <t>210906</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>39,61%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>63966</t>
+          <t>60260</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>112771</t>
+          <t>112187</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>100414</t>
+          <t>101797</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>130137</t>
+          <t>129402</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>179111</t>
+          <t>172806</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>236039</t>
+          <t>230690</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>43,33%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>22935</t>
+          <t>23898</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>45156</t>
+          <t>45198</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>36028</t>
+          <t>35108</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>58322</t>
+          <t>57106</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>63763</t>
+          <t>64375</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>96098</t>
+          <t>96832</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>19490</t>
+          <t>20236</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>39998</t>
+          <t>40142</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>20084</t>
+          <t>20098</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>38204</t>
+          <t>38123</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>46140</t>
+          <t>45025</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>73063</t>
+          <t>73119</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/AIRE_2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_2-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1939</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6031</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,15%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,9%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3891</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1279</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9554</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9,45%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>23,2%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>4175</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6069</t>
+          <t>9913</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5946</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11513</t>
+          <t>12008</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7390</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3913</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13142</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>15,8%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8,37%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>28,1%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>8995</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5708</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>13579</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>21,85%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>13,86%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>32,98%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8390</t>
+          <t>8622</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4639</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14956</t>
+          <t>13612</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>17386</t>
+          <t>16012</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11910</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23955</t>
+          <t>23011</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20520</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>15251</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>26954</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>43,88%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>32,61%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>57,64%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15307</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>10960</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>20109</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>37,18%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>26,62%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>48,84%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20749</t>
+          <t>15327</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14791</t>
+          <t>10790</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26595</t>
+          <t>20150</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>36057</t>
+          <t>35847</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28371</t>
+          <t>28166</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>44154</t>
+          <t>44161</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>50,03%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8492</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4092</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13768</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>18,16%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8,75%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>29,44%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4540</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2059</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9066</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>11,03%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>22,02%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8148</t>
+          <t>4776</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>2142</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13327</t>
+          <t>9328</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>12688</t>
+          <t>13268</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7748</t>
+          <t>7728</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19733</t>
+          <t>20147</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8424</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4414</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13671</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>18,01%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>9,44%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>29,23%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>8441</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4843</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>13069</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>20,5%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11,76%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>31,74%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9554</t>
+          <t>8610</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15714</t>
+          <t>13271</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>17996</t>
+          <t>17034</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12305</t>
+          <t>11143</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24564</t>
+          <t>24012</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,2%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>46765</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>46765</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>46765</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>41175</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>41175</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>41175</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48897</t>
+          <t>41510</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48897</t>
+          <t>41510</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48897</t>
+          <t>41510</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>90073</t>
+          <t>88274</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>90073</t>
+          <t>88274</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>90073</t>
+          <t>88274</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7015</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3289</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12887</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,6%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,96%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5184</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2236</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9707</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,98%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3785</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14715</t>
+          <t>10395</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>13041</t>
+          <t>12015</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7673</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20260</t>
+          <t>19492</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>16599</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>11145</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>23712</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>17,98%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>12,07%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>25,68%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>11884</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>7776</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>18103</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>18,34%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>12,0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>27,93%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18385</t>
+          <t>11774</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12587</t>
+          <t>7368</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26694</t>
+          <t>17510</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>30269</t>
+          <t>28373</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23166</t>
+          <t>20506</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>41479</t>
+          <t>37678</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>24,08%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>38039</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>30198</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>46555</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>41,19%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>32,7%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>50,42%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>32471</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>25944</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>38663</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>50,1%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>40,03%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>59,65%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>42062</t>
+          <t>31814</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32966</t>
+          <t>25652</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51126</t>
+          <t>38048</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>74533</t>
+          <t>69852</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>64219</t>
+          <t>58663</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>85651</t>
+          <t>81544</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>52,11%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>22413</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15468</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>30492</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>24,27%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>16,75%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>33,02%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>9772</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5765</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>15106</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>15,08%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,89%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>23,31%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22238</t>
+          <t>9742</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15352</t>
+          <t>5665</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30502</t>
+          <t>14599</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>32010</t>
+          <t>32155</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24271</t>
+          <t>23897</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42140</t>
+          <t>42382</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>27,08%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8274</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4281</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>14426</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>8,96%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4,64%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>15,62%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>5506</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2672</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10062</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>8,49%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>15,52%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>5828</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>10377</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>14107</t>
+          <t>14102</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>8977</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20602</t>
+          <t>20751</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>92340</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>92340</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>92340</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>64816</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>64816</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>64816</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>99144</t>
+          <t>64158</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>99144</t>
+          <t>64158</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>99144</t>
+          <t>64158</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>163960</t>
+          <t>156497</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>163960</t>
+          <t>156497</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>163960</t>
+          <t>156497</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4609</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10285</t>
+          <t>9794</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5204</t>
+          <t>4943</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10159</t>
+          <t>9755</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>9813</t>
+          <t>9537</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4792</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17684</t>
+          <t>15773</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>20313</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>14351</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>26863</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>35,64%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>25,18%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>47,13%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>41474</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>19801</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>62518</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>54,97%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>26,24%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>82,86%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>24286</t>
+          <t>13871</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16547</t>
+          <t>8866</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31893</t>
+          <t>20984</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>65760</t>
+          <t>34184</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43326</t>
+          <t>25563</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>101934</t>
+          <t>42750</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>41,3%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>25392</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>17976</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>32033</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>44,55%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>31,54%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>56,2%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>19979</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>7170</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34511</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>26,48%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>9,5%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>45,74%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>28589</t>
+          <t>18044</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21212</t>
+          <t>12445</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>36682</t>
+          <t>24524</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>48568</t>
+          <t>43436</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25692</t>
+          <t>34840</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>65322</t>
+          <t>53202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>51,4%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>6398</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2822</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>12834</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>11,22%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>22,52%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>6205</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1457</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>12256</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>8,22%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>16,24%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>6295</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12341</t>
+          <t>11109</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>12547</t>
+          <t>12693</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5830</t>
+          <t>7386</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20476</t>
+          <t>20198</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1548</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>3182</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>492</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>8214</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>4,22%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>10,89%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>926</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2246</t>
+          <t>7877</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8478</t>
+          <t>8701</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>56994</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>56994</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>56994</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>75450</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>75450</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>75450</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>64816</t>
+          <t>46519</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64816</t>
+          <t>46519</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64816</t>
+          <t>46519</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>140266</t>
+          <t>103513</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>140266</t>
+          <t>103513</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>140266</t>
+          <t>103513</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>4340</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1771</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>9971</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>6,85%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>15,74%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2097</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5772</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>8,16%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>2143</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>494</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10331</t>
+          <t>6157</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>6832</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13253</t>
+          <t>12480</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>18110</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>12023</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>24392</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>28,59%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>18,98%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>38,51%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>14314</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>9404</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>22941</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>20,25%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>13,3%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>32,45%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>19910</t>
+          <t>12314</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13775</t>
+          <t>7795</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>27300</t>
+          <t>18455</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>34224</t>
+          <t>30424</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25793</t>
+          <t>23155</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>44375</t>
+          <t>39879</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>30,38%</t>
         </is>
       </c>
     </row>
@@ -2992,107 +2992,107 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>22643</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>16639</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>29466</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>35,75%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>26,27%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>46,53%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>26831</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>20227</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>34108</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>37,95%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>28,61%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>48,24%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>23938</t>
+          <t>26770</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17087</t>
+          <t>20598</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30990</t>
+          <t>33623</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
+          <t>49,49%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>49413</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>39882</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>60347</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>37,64%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>30,38%</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
           <t>45,97%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>50769</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>41653</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>60662</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>36,76%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>30,16%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>43,92%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>9212</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>5022</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>14842</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>14,55%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>7,93%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>23,43%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>14305</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>9536</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>20993</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>20,23%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>13,49%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>29,69%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>9504</t>
+          <t>14252</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>9181</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15499</t>
+          <t>20927</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>23809</t>
+          <t>23464</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16730</t>
+          <t>15725</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>32175</t>
+          <t>31474</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>9027</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>4491</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>15053</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>14,25%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>7,09%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>23,77%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>13151</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>7904</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>19659</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>18,6%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>11,18%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>27,81%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>9329</t>
+          <t>12453</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>7429</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15467</t>
+          <t>18233</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>22481</t>
+          <t>21480</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>15850</t>
+          <t>14823</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>30782</t>
+          <t>29921</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,79%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>63332</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>63332</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>63332</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>70699</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>70699</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>70699</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>67415</t>
+          <t>67933</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>67415</t>
+          <t>67933</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>67415</t>
+          <t>67933</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>138114</t>
+          <t>131264</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>138114</t>
+          <t>131264</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>138114</t>
+          <t>131264</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>17887</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>11365</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>26633</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>6,89%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>4,38%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>10,27%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>15781</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>9154</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>24443</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>6,26%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>3,63%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>9,69%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>19851</t>
+          <t>16261</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13446</t>
+          <t>10727</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>29446</t>
+          <t>24564</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>35632</t>
+          <t>34148</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>25795</t>
+          <t>24846</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>46620</t>
+          <t>45405</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>62411</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>51807</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>75490</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>24,06%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>19,97%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>29,1%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>76668</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>51338</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>142413</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>30,41%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>20,36%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>56,48%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>70971</t>
+          <t>46581</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>58500</t>
+          <t>37123</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>85366</t>
+          <t>57781</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>147639</t>
+          <t>108992</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>121665</t>
+          <t>93544</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>210906</t>
+          <t>126008</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>106593</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>91276</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>120418</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>41,09%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>35,18%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>46,42%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>94588</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>60260</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>112187</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>37,51%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>23,9%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>44,49%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>115337</t>
+          <t>91955</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>101797</t>
+          <t>80074</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>129402</t>
+          <t>104040</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>209926</t>
+          <t>198547</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>172806</t>
+          <t>180456</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>230690</t>
+          <t>216630</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>45,17%</t>
         </is>
       </c>
     </row>
@@ -3787,67 +3787,67 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>46515</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>35486</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>58749</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>17,93%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>13,68%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>22,65%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>34821</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>23898</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>45198</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>13,81%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>9,48%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>17,93%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>46232</t>
+          <t>35066</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>35108</t>
+          <t>26868</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>57106</t>
+          <t>44866</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>81054</t>
+          <t>81581</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>64375</t>
+          <t>68910</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>96832</t>
+          <t>96798</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>26023</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>18805</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>35751</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>10,03%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>7,25%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>13,78%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>30281</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>20236</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>40142</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>12,01%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>8,03%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>15,92%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>27881</t>
+          <t>30258</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>20098</t>
+          <t>22842</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>38123</t>
+          <t>39824</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>58162</t>
+          <t>56280</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>45025</t>
+          <t>45226</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>73119</t>
+          <t>69207</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>259429</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>259429</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>259429</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>344</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>252140</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>252140</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>252140</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>280272</t>
+          <t>220120</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>280272</t>
+          <t>220120</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>280272</t>
+          <t>220120</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>532412</t>
+          <t>479549</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>532412</t>
+          <t>479549</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>532412</t>
+          <t>479549</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
